--- a/downloads/annee-creation.xlsx
+++ b/downloads/annee-creation.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Données" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données'!$A$1:$B$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données'!$A$1:$B$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -454,7 +454,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1885</v>
+        <v>1891</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -462,7 +462,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1891</v>
+        <v>1895</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -470,7 +470,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -478,23 +478,23 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1897</v>
+        <v>1904</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1904</v>
+        <v>1923</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
@@ -502,7 +502,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -510,7 +510,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1925</v>
+        <v>1928</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
@@ -518,7 +518,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>
@@ -526,7 +526,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="B12" t="n">
         <v>1</v>
@@ -534,7 +534,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1930</v>
+        <v>1936</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
@@ -542,7 +542,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1936</v>
+        <v>1943</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>
@@ -550,7 +550,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1942</v>
+        <v>1945</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1973</v>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -705,7 +705,7 @@
         <v>1976</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -729,7 +729,7 @@
         <v>1979</v>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -761,7 +761,7 @@
         <v>1984</v>
       </c>
       <c r="B41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -769,7 +769,7 @@
         <v>1985</v>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -785,7 +785,7 @@
         <v>1987</v>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -838,15 +838,15 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B52" t="n">
         <v>2</v>
@@ -854,15 +854,15 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B54" t="n">
         <v>3</v>
@@ -870,31 +870,31 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="B55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B58" t="n">
         <v>3</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B59" t="n">
         <v>3</v>
@@ -910,95 +910,95 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B65" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B68" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B69" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B71" t="n">
         <v>2</v>
@@ -1006,86 +1006,94 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B76" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B81" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
         <v>2025</v>
       </c>
-      <c r="B81" t="n">
+      <c r="B82" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B81"/>
+  <autoFilter ref="A1:B82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>